--- a/INSTANCES/instances_literature_xlsx/A_MTN_8/667FL_20A_4.xlsx
+++ b/INSTANCES/instances_literature_xlsx/A_MTN_8/667FL_20A_4.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="75">
   <si>
     <t>YEAR</t>
   </si>
@@ -178,42 +178,6 @@
   </si>
   <si>
     <t>T_7</t>
-  </si>
-  <si>
-    <t>ADF</t>
-  </si>
-  <si>
-    <t>AOE</t>
-  </si>
-  <si>
-    <t>BZI</t>
-  </si>
-  <si>
-    <t>CKZ</t>
-  </si>
-  <si>
-    <t>DLM</t>
-  </si>
-  <si>
-    <t>HTY</t>
-  </si>
-  <si>
-    <t>KCM</t>
-  </si>
-  <si>
-    <t>KYA</t>
-  </si>
-  <si>
-    <t>NAJ</t>
-  </si>
-  <si>
-    <t>TEQ</t>
-  </si>
-  <si>
-    <t>XHQ</t>
-  </si>
-  <si>
-    <t>YEI</t>
   </si>
   <si>
     <t>TAIL_NUMBER</t>
@@ -18092,7 +18056,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -18126,25 +18090,25 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -18152,908 +18116,102 @@
         <v>12</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8">
-        <v>3</v>
-      </c>
-      <c r="F8">
-        <v>2</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9">
-        <v>3</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>3</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>2</v>
-      </c>
-      <c r="D10">
-        <v>2</v>
-      </c>
-      <c r="E10">
-        <v>3</v>
-      </c>
-      <c r="F10">
-        <v>3</v>
-      </c>
-      <c r="G10">
-        <v>3</v>
-      </c>
-      <c r="H10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>2</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12">
-        <v>2</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>2</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>3</v>
-      </c>
-      <c r="H12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13">
-        <v>2</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>2</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>3</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="D14">
-        <v>2</v>
-      </c>
-      <c r="E14">
-        <v>3</v>
-      </c>
-      <c r="F14">
-        <v>3</v>
-      </c>
-      <c r="G14">
-        <v>3</v>
-      </c>
-      <c r="H14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" t="s">
-        <v>54</v>
-      </c>
-      <c r="B15">
-        <v>2</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>2</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>3</v>
-      </c>
-      <c r="H15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>2</v>
-      </c>
-      <c r="G16">
-        <v>2</v>
-      </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17">
-        <v>2</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>2</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>3</v>
-      </c>
-      <c r="H17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18">
-        <v>2</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>2</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>3</v>
-      </c>
-      <c r="H18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>2</v>
-      </c>
-      <c r="E19">
-        <v>3</v>
-      </c>
-      <c r="F19">
-        <v>2</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20">
-        <v>3</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20">
-        <v>2</v>
-      </c>
-      <c r="H20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" t="s">
-        <v>17</v>
-      </c>
-      <c r="B21">
-        <v>2</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>2</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>3</v>
-      </c>
-      <c r="H21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22">
-        <v>2</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>3</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-      <c r="H22">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23">
-        <v>2</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>2</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>3</v>
-      </c>
-      <c r="H23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24">
-        <v>3</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24">
-        <v>2</v>
-      </c>
-      <c r="H24">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" t="s">
-        <v>57</v>
-      </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25">
-        <v>2</v>
-      </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-      <c r="E25">
-        <v>3</v>
-      </c>
-      <c r="F25">
-        <v>3</v>
-      </c>
-      <c r="G25">
-        <v>3</v>
-      </c>
-      <c r="H25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26">
-        <v>2</v>
-      </c>
-      <c r="C26">
-        <v>2</v>
-      </c>
-      <c r="D26">
-        <v>3</v>
-      </c>
-      <c r="E26">
-        <v>3</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27">
-        <v>2</v>
-      </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-      <c r="E27">
-        <v>2</v>
-      </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-      <c r="H27">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28">
-        <v>3</v>
-      </c>
-      <c r="E28">
-        <v>1</v>
-      </c>
-      <c r="F28">
-        <v>3</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29">
-        <v>2</v>
-      </c>
-      <c r="C29">
-        <v>0</v>
-      </c>
-      <c r="D29">
-        <v>2</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
-      <c r="G29">
-        <v>3</v>
-      </c>
-      <c r="H29">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30">
-        <v>0</v>
-      </c>
-      <c r="C30">
-        <v>2</v>
-      </c>
-      <c r="D30">
-        <v>3</v>
-      </c>
-      <c r="E30">
-        <v>2</v>
-      </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30">
-        <v>2</v>
-      </c>
-      <c r="H30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" t="s">
-        <v>19</v>
-      </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="C31">
-        <v>1</v>
-      </c>
-      <c r="D31">
-        <v>3</v>
-      </c>
-      <c r="E31">
-        <v>1</v>
-      </c>
-      <c r="F31">
-        <v>3</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" t="s">
-        <v>59</v>
-      </c>
-      <c r="B32">
-        <v>3</v>
-      </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32">
-        <v>1</v>
-      </c>
-      <c r="G32">
-        <v>2</v>
-      </c>
-      <c r="H32">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" t="s">
-        <v>20</v>
-      </c>
-      <c r="B33">
-        <v>0</v>
-      </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
-      <c r="E33">
-        <v>3</v>
-      </c>
-      <c r="F33">
-        <v>2</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" t="s">
-        <v>22</v>
-      </c>
-      <c r="B34">
-        <v>0</v>
-      </c>
-      <c r="C34">
-        <v>0</v>
-      </c>
-      <c r="D34">
-        <v>2</v>
-      </c>
-      <c r="E34">
-        <v>3</v>
-      </c>
-      <c r="F34">
-        <v>2</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B35">
-        <v>3</v>
-      </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35">
-        <v>2</v>
-      </c>
-      <c r="E35">
-        <v>1</v>
-      </c>
-      <c r="F35">
-        <v>3</v>
-      </c>
-      <c r="G35">
-        <v>1</v>
-      </c>
-      <c r="H35">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" t="s">
-        <v>60</v>
-      </c>
-      <c r="B36">
-        <v>2</v>
-      </c>
-      <c r="C36">
-        <v>0</v>
-      </c>
-      <c r="D36">
-        <v>2</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36">
-        <v>0</v>
-      </c>
-      <c r="G36">
-        <v>3</v>
-      </c>
-      <c r="H36">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" t="s">
-        <v>61</v>
-      </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-      <c r="C37">
-        <v>2</v>
-      </c>
-      <c r="D37">
-        <v>3</v>
-      </c>
-      <c r="E37">
-        <v>2</v>
-      </c>
-      <c r="F37">
-        <v>0</v>
-      </c>
-      <c r="G37">
-        <v>2</v>
-      </c>
-      <c r="H37">
         <v>1</v>
       </c>
     </row>
@@ -19069,24 +18227,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="B1" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C1" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E1" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
@@ -19103,7 +18261,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
@@ -19120,7 +18278,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
@@ -19137,7 +18295,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
@@ -19154,7 +18312,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
@@ -19171,7 +18329,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
@@ -19188,7 +18346,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
@@ -19205,7 +18363,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -19222,7 +18380,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s">
         <v>20</v>
@@ -19239,7 +18397,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -19256,7 +18414,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
@@ -19273,7 +18431,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
@@ -19290,7 +18448,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B14" t="s">
         <v>10</v>
@@ -19307,7 +18465,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="B15" t="s">
         <v>11</v>
@@ -19324,7 +18482,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
@@ -19341,7 +18499,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="B17" t="s">
         <v>16</v>
@@ -19358,7 +18516,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="B18" t="s">
         <v>11</v>
@@ -19375,7 +18533,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="B19" t="s">
         <v>10</v>
@@ -19392,7 +18550,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="B20" t="s">
         <v>10</v>
@@ -19409,7 +18567,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="B21" t="s">
         <v>8</v>

--- a/INSTANCES/instances_literature_xlsx/A_MTN_8/667FL_20A_4.xlsx
+++ b/INSTANCES/instances_literature_xlsx/A_MTN_8/667FL_20A_4.xlsx
@@ -18028,10 +18028,10 @@
         <v>480</v>
       </c>
       <c r="D2">
-        <v>50</v>
+        <v>76.0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>16.0</v>
       </c>
       <c r="F2">
         <v>7</v>
@@ -18102,7 +18102,7 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -18157,7 +18157,7 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -18174,19 +18174,19 @@
         <v>5</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -18253,10 +18253,10 @@
         <v>5780</v>
       </c>
       <c r="D2">
-        <v>49.0</v>
+        <v>74.0</v>
       </c>
       <c r="E2">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -18270,10 +18270,10 @@
         <v>5440</v>
       </c>
       <c r="D3">
-        <v>46.0</v>
+        <v>69.0</v>
       </c>
       <c r="E3">
-        <v>10.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -18287,10 +18287,10 @@
         <v>5260</v>
       </c>
       <c r="D4">
-        <v>44.0</v>
+        <v>67.0</v>
       </c>
       <c r="E4">
-        <v>9.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -18304,10 +18304,10 @@
         <v>5075</v>
       </c>
       <c r="D5">
-        <v>43.0</v>
+        <v>65.0</v>
       </c>
       <c r="E5">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -18321,10 +18321,10 @@
         <v>4890</v>
       </c>
       <c r="D6">
-        <v>41.0</v>
+        <v>62.0</v>
       </c>
       <c r="E6">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -18338,10 +18338,10 @@
         <v>4340</v>
       </c>
       <c r="D7">
-        <v>37.0</v>
+        <v>55.0</v>
       </c>
       <c r="E7">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -18355,10 +18355,10 @@
         <v>4305</v>
       </c>
       <c r="D8">
-        <v>36.0</v>
+        <v>55.0</v>
       </c>
       <c r="E8">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -18372,10 +18372,10 @@
         <v>4005</v>
       </c>
       <c r="D9">
-        <v>34.0</v>
+        <v>51.0</v>
       </c>
       <c r="E9">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
